--- a/sample_outputs/demo_prod.xlsx
+++ b/sample_outputs/demo_prod.xlsx
@@ -8,28 +8,31 @@
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
-    <sheet name="Dimensions" sheetId="2" r:id="rId2"/>
-    <sheet name="Metrics" sheetId="3" r:id="rId3"/>
-    <sheet name="Segments" sheetId="4" r:id="rId4"/>
-    <sheet name="Calculated Metrics" sheetId="5" r:id="rId5"/>
-    <sheet name="Virtual Report Suites" sheetId="6" r:id="rId6"/>
-    <sheet name="Classifications" sheetId="7" r:id="rId7"/>
+    <sheet name="Coverage" sheetId="2" r:id="rId2"/>
+    <sheet name="Quality" sheetId="3" r:id="rId3"/>
+    <sheet name="Dimensions" sheetId="4" r:id="rId4"/>
+    <sheet name="Metrics" sheetId="5" r:id="rId5"/>
+    <sheet name="Segments" sheetId="6" r:id="rId6"/>
+    <sheet name="Calculated Metrics" sheetId="7" r:id="rId7"/>
+    <sheet name="Virtual Report Suites" sheetId="8" r:id="rId8"/>
+    <sheet name="Classifications" sheetId="9" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Calculated Metrics'!$A$1:$L$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Classifications!$A$1:$D$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Dimensions!$A$1:$I$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Metrics!$A$1:$J$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Segments!$A$1:$K$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Calculated Metrics'!$A$1:$L$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">Classifications!$A$1:$D$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Coverage!$A$1:$D$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Dimensions!$A$1:$I$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Metrics!$A$1:$J$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Segments!$A$1:$K$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Summary!$A$1:$B$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Virtual Report Suites'!$A$1:$I$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Virtual Report Suites'!$A$1:$I$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="105">
   <si>
     <t>Field</t>
   </si>
@@ -83,6 +86,24 @@
   </si>
   <si>
     <t>1.0.0</t>
+  </si>
+  <si>
+    <t>Family</t>
+  </si>
+  <si>
+    <t>State</t>
+  </si>
+  <si>
+    <t>Count</t>
+  </si>
+  <si>
+    <t>Expansion Level</t>
+  </si>
+  <si>
+    <t>Collected</t>
+  </si>
+  <si>
+    <t>No quality audit ran.</t>
   </si>
   <si>
     <t>id</t>
@@ -332,16 +353,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -357,7 +370,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -365,30 +378,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -691,10 +686,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
     </row>
@@ -793,6 +788,121 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="11.7109375" customWidth="1"/>
+    <col min="3" max="3" width="7.7109375" customWidth="1"/>
+    <col min="4" max="4" width="17.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:D7"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -808,127 +918,127 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G1" s="1" t="s">
+      <c r="A1" t="s">
         <v>24</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="B1" t="s">
         <v>25</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="C1" t="s">
         <v>26</v>
+      </c>
+      <c r="D1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B2" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="C2" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D2" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F2" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="G2" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="H2" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="I2" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="B3" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C3" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D3" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F3" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="H3" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="I3" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="B4" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="C4" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F4" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="H4" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="I4" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C5" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D5" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F5" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="G5" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="H5" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="I5" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -937,7 +1047,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J4"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -955,122 +1065,122 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G1" s="1" t="s">
+      <c r="A1" t="s">
         <v>24</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="B1" t="s">
         <v>25</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="J1" s="1" t="s">
+      <c r="C1" t="s">
         <v>26</v>
+      </c>
+      <c r="D1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I1" t="s">
+        <v>54</v>
+      </c>
+      <c r="J1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E2" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2" t="s">
+        <v>46</v>
+      </c>
+      <c r="G2" t="s">
+        <v>65</v>
+      </c>
+      <c r="H2" t="s">
         <v>49</v>
       </c>
-      <c r="B2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D2" t="s">
-        <v>56</v>
-      </c>
-      <c r="E2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F2" t="s">
-        <v>40</v>
-      </c>
-      <c r="G2" t="s">
-        <v>59</v>
-      </c>
-      <c r="H2" t="s">
-        <v>43</v>
-      </c>
       <c r="I2" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="J2" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="B3" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="C3" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="D3" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="E3" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="F3" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="G3" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="H3" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="J3" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E4" t="s">
+        <v>64</v>
+      </c>
+      <c r="F4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H4" t="s">
+        <v>49</v>
+      </c>
+      <c r="J4" t="s">
         <v>51</v>
-      </c>
-      <c r="B4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D4" t="s">
-        <v>57</v>
-      </c>
-      <c r="E4" t="s">
-        <v>58</v>
-      </c>
-      <c r="F4" t="s">
-        <v>40</v>
-      </c>
-      <c r="H4" t="s">
-        <v>43</v>
-      </c>
-      <c r="J4" t="s">
-        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -1079,7 +1189,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K3"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1097,99 +1207,99 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="A1" t="s">
         <v>24</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="H1" s="1" t="s">
+      <c r="B1" t="s">
         <v>25</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>26</v>
+      <c r="C1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I1" t="s">
+        <v>71</v>
+      </c>
+      <c r="J1" t="s">
+        <v>72</v>
+      </c>
+      <c r="K1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="B2" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="D2" t="s">
         <v>13</v>
       </c>
       <c r="E2" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="F2" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G2" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="H2" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="I2" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="J2" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K2" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="D3" t="s">
         <v>13</v>
       </c>
       <c r="E3" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="F3" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G3" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="H3" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="K3" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -1198,7 +1308,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L2"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1217,79 +1327,79 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="A1" t="s">
         <v>24</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="J1" s="1" t="s">
+      <c r="B1" t="s">
         <v>25</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="L1" s="1" t="s">
+      <c r="C1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1" t="s">
+        <v>83</v>
+      </c>
+      <c r="G1" t="s">
+        <v>52</v>
+      </c>
+      <c r="H1" t="s">
         <v>26</v>
+      </c>
+      <c r="I1" t="s">
+        <v>69</v>
+      </c>
+      <c r="J1" t="s">
+        <v>31</v>
+      </c>
+      <c r="K1" t="s">
+        <v>84</v>
+      </c>
+      <c r="L1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="B2" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="C2" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="D2" t="s">
         <v>13</v>
       </c>
       <c r="E2" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="F2" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="G2" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="H2" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="I2" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="J2" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="K2" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="L2" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -1298,7 +1408,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I2"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1315,61 +1425,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="A1" t="s">
         <v>24</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>26</v>
+      <c r="B1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1" t="s">
+        <v>72</v>
+      </c>
+      <c r="I1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B2" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="C2" t="s">
         <v>13</v>
       </c>
       <c r="D2" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="E2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="F2" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="G2" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="H2" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="I2" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -1378,7 +1488,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1390,31 +1500,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>26</v>
+      <c r="A1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="B2" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="C2" t="s">
         <v>13</v>
       </c>
       <c r="D2" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/sample_outputs/demo_prod.xlsx
+++ b/sample_outputs/demo_prod.xlsx
@@ -16,14 +16,16 @@
     <sheet name="Calculated Metrics" sheetId="7" r:id="rId7"/>
     <sheet name="Virtual Report Suites" sheetId="8" r:id="rId8"/>
     <sheet name="Classifications" sheetId="9" r:id="rId9"/>
+    <sheet name="References" sheetId="10" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Calculated Metrics'!$A$1:$L$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Calculated Metrics'!$A$1:$O$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">Classifications!$A$1:$D$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Coverage!$A$1:$D$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Dimensions!$A$1:$I$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Metrics!$A$1:$J$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Segments!$A$1:$K$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">References!$A$1:$I$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Segments!$A$1:$N$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Summary!$A$1:$B$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Virtual Report Suites'!$A$1:$I$2</definedName>
   </definedNames>
@@ -32,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="127">
   <si>
     <t>Field</t>
   </si>
@@ -253,6 +255,15 @@
     <t>modified</t>
   </si>
   <si>
+    <t>definition_summary</t>
+  </si>
+  <si>
+    <t>metric_references</t>
+  </si>
+  <si>
+    <t>segment_references</t>
+  </si>
+  <si>
     <t>s_111</t>
   </si>
   <si>
@@ -271,10 +282,10 @@
     <t>42</t>
   </si>
   <si>
-    <t>{"container": {"context": "hits", "func": "container", "pred": {"func": "eq", "val": "mobile"}}, "version": [1, 0, 0]}</t>
-  </si>
-  <si>
-    <t>{"container": {"context": "visits", "func": "container", "pred": {"func": "eq", "val": "returning"}}, "version": [1, 0, 0]}</t>
+    <t>{"container": {"context": "hits", "func": "container", "pred": {"func": "streq", "str": "mobile", "val": {"func": "attr", "name": "variables/evar2"}}}, "func": "segment", "version": [1, 0, 0]}</t>
+  </si>
+  <si>
+    <t>{"container": {"context": "visits", "func": "container", "pred": {"func": "and", "preds": [{"func": "gt", "num": 1, "val": {"func": "attr", "name": "variables/visitnumber"}}, {"evt": {"func": "event", "name": "metrics/pageviews"}, "func": "event-exists"}]}}, "func": "segment", "version": [1, 0, 0]}</t>
   </si>
   <si>
     <t>2025-01-01T00:00:00Z</t>
@@ -283,12 +294,21 @@
     <t>2025-01-02T00:00:00Z</t>
   </si>
   <si>
+    <t>Hit where variables/evar2 = 'mobile'</t>
+  </si>
+  <si>
+    <t>Visit where variables/visitnumber &gt; 1 AND metrics/pageviews exists</t>
+  </si>
+  <si>
     <t>polarity</t>
   </si>
   <si>
     <t>categories</t>
   </si>
   <si>
+    <t>formula_summary</t>
+  </si>
+  <si>
     <t>cm_1</t>
   </si>
   <si>
@@ -307,12 +327,18 @@
     <t>decimal</t>
   </si>
   <si>
-    <t>{"formula": {"args": ["metrics/orders", "metrics/visits"], "func": "divide"}}</t>
+    <t>{"formula": {"col1": {"func": "metric", "name": "metrics/orders"}, "col2": {"func": "segment", "metric": {"func": "metric", "name": "metrics/visits"}, "segment_id": "s_222"}, "func": "divide"}, "func": "calc-metric", "version": [1, 0, 0]}</t>
   </si>
   <si>
     <t>["Conversion"]</t>
   </si>
   <si>
+    <t>metrics/orders / metrics/visits[segment s_222]</t>
+  </si>
+  <si>
+    <t>metrics/orders, metrics/visits</t>
+  </si>
+  <si>
     <t>parent_rsid</t>
   </si>
   <si>
@@ -347,6 +373,48 @@
   </si>
   <si>
     <t>Campaign Metadata</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Relation</t>
+  </si>
+  <si>
+    <t>Kind</t>
+  </si>
+  <si>
+    <t>Target Family</t>
+  </si>
+  <si>
+    <t>Target ID</t>
+  </si>
+  <si>
+    <t>Target Name</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>references</t>
+  </si>
+  <si>
+    <t>referenced by</t>
+  </si>
+  <si>
+    <t>metric</t>
+  </si>
+  <si>
+    <t>segment</t>
+  </si>
+  <si>
+    <t>s_eu</t>
+  </si>
+  <si>
+    <t>resolved</t>
+  </si>
+  <si>
+    <t>unresolved</t>
   </si>
 </sst>
 </file>
@@ -787,6 +855,222 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="8.7109375" customWidth="1"/>
+    <col min="3" max="3" width="20.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="9.7109375" customWidth="1"/>
+    <col min="6" max="6" width="20.7109375" customWidth="1"/>
+    <col min="7" max="7" width="19.7109375" customWidth="1"/>
+    <col min="8" max="8" width="20.7109375" customWidth="1"/>
+    <col min="9" max="9" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F1" t="s">
+        <v>116</v>
+      </c>
+      <c r="G1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H1" t="s">
+        <v>118</v>
+      </c>
+      <c r="I1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E2" t="s">
+        <v>122</v>
+      </c>
+      <c r="F2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" t="s">
+        <v>55</v>
+      </c>
+      <c r="H2" t="s">
+        <v>58</v>
+      </c>
+      <c r="I2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D3" t="s">
+        <v>120</v>
+      </c>
+      <c r="E3" t="s">
+        <v>122</v>
+      </c>
+      <c r="F3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G3" t="s">
+        <v>57</v>
+      </c>
+      <c r="H3" t="s">
+        <v>60</v>
+      </c>
+      <c r="I3" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" t="s">
+        <v>91</v>
+      </c>
+      <c r="C4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D4" t="s">
+        <v>120</v>
+      </c>
+      <c r="E4" t="s">
+        <v>123</v>
+      </c>
+      <c r="F4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4" t="s">
+        <v>77</v>
+      </c>
+      <c r="H4" t="s">
+        <v>79</v>
+      </c>
+      <c r="I4" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>77</v>
+      </c>
+      <c r="C5" t="s">
+        <v>79</v>
+      </c>
+      <c r="D5" t="s">
+        <v>120</v>
+      </c>
+      <c r="E5" t="s">
+        <v>122</v>
+      </c>
+      <c r="F5" t="s">
+        <v>8</v>
+      </c>
+      <c r="G5" t="s">
+        <v>56</v>
+      </c>
+      <c r="H5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I5" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C6" t="s">
+        <v>79</v>
+      </c>
+      <c r="D6" t="s">
+        <v>121</v>
+      </c>
+      <c r="F6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6" t="s">
+        <v>91</v>
+      </c>
+      <c r="H6" t="s">
+        <v>92</v>
+      </c>
+      <c r="I6" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>105</v>
+      </c>
+      <c r="C7" t="s">
+        <v>106</v>
+      </c>
+      <c r="D7" t="s">
+        <v>120</v>
+      </c>
+      <c r="E7" t="s">
+        <v>123</v>
+      </c>
+      <c r="G7" t="s">
+        <v>124</v>
+      </c>
+      <c r="I7" t="s">
+        <v>126</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:I7"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D7"/>
@@ -1191,7 +1475,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7.7109375" customWidth="1"/>
@@ -1204,9 +1488,12 @@
     <col min="8" max="8" width="6.7109375" customWidth="1"/>
     <col min="9" max="10" width="22.7109375" customWidth="1"/>
     <col min="11" max="11" width="7.7109375" customWidth="1"/>
+    <col min="12" max="12" width="60.7109375" customWidth="1"/>
+    <col min="13" max="13" width="19.7109375" customWidth="1"/>
+    <col min="14" max="14" width="20.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:14">
       <c r="A1" t="s">
         <v>24</v>
       </c>
@@ -1240,25 +1527,34 @@
       <c r="K1" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1" t="s">
+        <v>73</v>
+      </c>
+      <c r="M1" t="s">
+        <v>74</v>
+      </c>
+      <c r="N1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C2" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D2" t="s">
         <v>13</v>
       </c>
       <c r="E2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="G2" t="s">
         <v>51</v>
@@ -1267,30 +1563,33 @@
         <v>49</v>
       </c>
       <c r="I2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="J2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="K2" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="3" spans="1:11">
+      <c r="L2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D3" t="s">
         <v>13</v>
       </c>
       <c r="E3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="G3" t="s">
         <v>51</v>
@@ -1301,16 +1600,22 @@
       <c r="K3" t="s">
         <v>51</v>
       </c>
+      <c r="L3" t="s">
+        <v>87</v>
+      </c>
+      <c r="M3" t="s">
+        <v>56</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K3"/>
+  <autoFilter ref="A1:N3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="6.7109375" customWidth="1"/>
@@ -1324,9 +1629,12 @@
     <col min="10" max="10" width="6.7109375" customWidth="1"/>
     <col min="11" max="11" width="16.7109375" customWidth="1"/>
     <col min="12" max="12" width="7.7109375" customWidth="1"/>
+    <col min="13" max="13" width="48.7109375" customWidth="1"/>
+    <col min="14" max="14" width="32.7109375" customWidth="1"/>
+    <col min="15" max="15" width="20.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:15">
       <c r="A1" t="s">
         <v>24</v>
       </c>
@@ -1343,7 +1651,7 @@
         <v>68</v>
       </c>
       <c r="F1" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="G1" t="s">
         <v>52</v>
@@ -1358,52 +1666,70 @@
         <v>31</v>
       </c>
       <c r="K1" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="L1" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="M1" t="s">
+        <v>90</v>
+      </c>
+      <c r="N1" t="s">
+        <v>74</v>
+      </c>
+      <c r="O1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="B2" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="C2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="D2" t="s">
         <v>13</v>
       </c>
       <c r="E2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F2" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="G2" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="H2" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="I2" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="J2" t="s">
         <v>49</v>
       </c>
       <c r="K2" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="L2" t="s">
         <v>51</v>
       </c>
+      <c r="M2" t="s">
+        <v>99</v>
+      </c>
+      <c r="N2" t="s">
+        <v>100</v>
+      </c>
+      <c r="O2" t="s">
+        <v>77</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L2"/>
+  <autoFilter ref="A1:O2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1432,19 +1758,19 @@
         <v>25</v>
       </c>
       <c r="C1" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="D1" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="E1" t="s">
         <v>30</v>
       </c>
       <c r="F1" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="G1" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="H1" t="s">
         <v>72</v>
@@ -1455,28 +1781,28 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="B2" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C2" t="s">
         <v>13</v>
       </c>
       <c r="D2" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="E2" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="F2" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="G2" t="s">
         <v>49</v>
       </c>
       <c r="H2" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="I2" t="s">
         <v>51</v>
@@ -1515,10 +1841,10 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="B2" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="C2" t="s">
         <v>13</v>
